--- a/data/trans_orig/cron_prev_index-Clase-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la prevalencia</t>
+          <t>Índice de cronicidad física en base a la prevalencia (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,47</t>
+          <t>0,33; 0,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,37 +726,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,55</t>
+          <t>0,38; 0,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,72</t>
+          <t>0,57; 0,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,5</t>
+          <t>0,31; 0,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,47</t>
+          <t>0,28; 0,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,52</t>
+          <t>0,34; 0,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,67</t>
+          <t>0,53; 0,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,46</t>
+          <t>0,34; 0,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,49</t>
+          <t>0,34; 0,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,76</t>
+          <t>0,59; 0,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,47</t>
+          <t>0,31; 0,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,61</t>
+          <t>0,48; 0,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,46</t>
+          <t>0,35; 0,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -996,42 +996,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,55</t>
+          <t>0,41; 0,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,78</t>
+          <t>0,61; 0,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,63</t>
+          <t>0,5; 0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,83</t>
+          <t>0,2; 0,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,73</t>
+          <t>0,45; 0,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,79</t>
+          <t>0,55; 0,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,96</t>
+          <t>0,6; 0,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,08</t>
+          <t>0,81; 1,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,77</t>
+          <t>0,61; 0,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,86</t>
+          <t>0,26; 0,85</t>
         </is>
       </c>
     </row>
@@ -1151,17 +1151,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,8</t>
+          <t>0,67; 0,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,61</t>
+          <t>0,48; 0,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,51</t>
+          <t>0,4; 0,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,04</t>
+          <t>0,61; 1,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,6</t>
+          <t>0,51; 0,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,52</t>
+          <t>0,67; 1,58</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,56</t>
+          <t>0,37; 0,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,69</t>
+          <t>0,52; 0,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,92</t>
+          <t>0,75; 0,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,83</t>
+          <t>0,68; 0,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,09</t>
+          <t>0,87; 1,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,78</t>
+          <t>0,66; 0,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,25</t>
+          <t>0,12; 0,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,25</t>
+          <t>0,13; 0,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,39</t>
+          <t>0,17; 0,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,08</t>
+          <t>0,94; 1,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 0,97</t>
+          <t>0,83; 0,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,78</t>
+          <t>0,67; 0,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,87</t>
+          <t>0,74; 0,88</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,57</t>
+          <t>0,51; 0,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,69</t>
+          <t>0,5; 0,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,32</t>
+          <t>0,79; 1,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,0</t>
+          <t>0,7; 1,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_prev_index-Clase-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Clase-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -726,22 +726,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,56</t>
+          <t>0,39; 0,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,73</t>
+          <t>0,58; 0,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,49</t>
+          <t>0,32; 0,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,48</t>
+          <t>0,28; 0,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,66</t>
+          <t>0,52; 0,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,45</t>
+          <t>0,35; 0,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,48</t>
+          <t>0,36; 0,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,67</t>
+          <t>0,58; 0,68</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -861,27 +861,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,5</t>
+          <t>0,34; 0,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,57</t>
+          <t>0,41; 0,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,76</t>
+          <t>0,59; 0,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,46</t>
+          <t>0,29; 0,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,49</t>
+          <t>0,31; 0,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,62</t>
+          <t>0,49; 0,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,67</t>
+          <t>0,56; 0,68</t>
         </is>
       </c>
     </row>
@@ -943,34 +943,34 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,67</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0,92</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0,68</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,54</t>
+          <t>0,41; 0,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,79</t>
+          <t>0,6; 0,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,64</t>
+          <t>0,49; 0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,83</t>
+          <t>0,68; 0,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,75</t>
+          <t>0,45; 0,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,79</t>
+          <t>0,56; 0,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,97</t>
+          <t>0,6; 1,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,1</t>
+          <t>0,79; 1,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,57</t>
+          <t>0,44; 0,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,75</t>
+          <t>0,61; 0,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,68</t>
+          <t>0,55; 0,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,85</t>
+          <t>0,74; 0,9</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1141,22 +1141,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,67</t>
+          <t>0,55; 0,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,63</t>
+          <t>0,52; 0,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,79</t>
+          <t>0,66; 0,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,63</t>
+          <t>0,47; 0,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,5</t>
+          <t>0,39; 0,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,86</t>
+          <t>0,57; 0,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,59</t>
+          <t>0,51; 0,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,58</t>
+          <t>0,64; 0,72</t>
         </is>
       </c>
     </row>
@@ -1223,27 +1223,27 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,68</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>0,75</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,88</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,68</t>
+          <t>0,53; 0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,85</t>
+          <t>0,61; 0,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,93</t>
+          <t>0,74; 0,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,83</t>
+          <t>0,67; 0,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,08</t>
+          <t>0,94; 1,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1326,19 +1326,19 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,74</t>
+          <t>0,63; 0,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 0,98</t>
+          <t>0,82; 0,93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,8</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,16</t>
+          <t>0,08; 0,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,4</t>
+          <t>0,15; 0,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 0,93</t>
+          <t>0,81; 0,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,08</t>
+          <t>0,92; 1,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 0,98</t>
+          <t>0,83; 0,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,06</t>
+          <t>0,88; 1,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,78</t>
+          <t>0,67; 0,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,81</t>
+          <t>0,69; 0,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,88</t>
+          <t>0,73; 0,86</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,57</t>
+          <t>0,5; 0,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,7</t>
+          <t>0,64; 0,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,34</t>
+          <t>0,76; 0,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,57</t>
+          <t>0,53; 0,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,01</t>
+          <t>0,71; 0,76</t>
         </is>
       </c>
     </row>
